--- a/data/tony/excel/12345679_2025_invoices.xlsx
+++ b/data/tony/excel/12345679_2025_invoices.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,19 +493,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>400000000000000</t>
+          <t>400000000000005</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>101401017</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>ΣΤΡΙΚΟΣ ΙΩΑΝΝ</t>
-        </is>
-      </c>
+          <t>801466788</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>ΑΛΠ</t>
@@ -513,12 +509,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>142362</t>
+          <t>61010</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>31/10/2025</t>
+          <t>15/09/2025</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -529,126 +525,18 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>30,00</t>
+          <t>14,9</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>30,00</t>
+          <t>14,9</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>142362</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>400000000000001</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>094475066</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>ΜΥΡΤΕΑ 106</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>ΑΛΠ</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2221034</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>14/10/2025</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>ΑΠΟΔΕΙΞΗ</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>2221034</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>400000000000002</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>999644611</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>ΕΚΟ ΗΛΙΟΥΠΟΛΗΣ (R020)</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>ΑΛΠ</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>1412560</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>14/10/2025</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>ΑΠΟΔΕΙΞΗ</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>1412560</t>
+          <t>61010</t>
         </is>
       </c>
     </row>
